--- a/branches/issue-91/ValueSet-BacterialCodes.xlsx
+++ b/branches/issue-91/ValueSet-BacterialCodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:00+00:00</t>
+    <t>2025-04-28T07:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
